--- a/result/Table202605.xlsx
+++ b/result/Table202605.xlsx
@@ -754,7 +754,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I7" t="n">
         <v>12.76</v>
       </c>
       <c r="J7" t="n">
-        <v>9.869999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="K7" t="n">
-        <v>-22.65</v>
+        <v>-23.51</v>
       </c>
       <c r="L7" t="n">
-        <v>-22648.9</v>
+        <v>-23510.97</v>
       </c>
     </row>
     <row r="8">
@@ -954,7 +954,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I11" t="n">
         <v>10.13</v>

--- a/result/Table202605.xlsx
+++ b/result/Table202605.xlsx
@@ -616,24 +616,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I4" t="n">
         <v>46.47</v>
       </c>
       <c r="J4" t="n">
-        <v>50.88</v>
+        <v>48.65</v>
       </c>
       <c r="K4" t="n">
-        <v>9.49</v>
+        <v>4.69</v>
       </c>
       <c r="L4" t="n">
-        <v>9489.99</v>
+        <v>4691.2</v>
       </c>
     </row>
     <row r="5">
@@ -708,24 +708,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I6" t="n">
         <v>26.53</v>
       </c>
       <c r="J6" t="n">
-        <v>26.17</v>
+        <v>23.52</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.36</v>
+        <v>-11.35</v>
       </c>
       <c r="L6" t="n">
-        <v>-1356.95</v>
+        <v>-11345.65</v>
       </c>
     </row>
     <row r="7">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I13" t="n">
         <v>64.39</v>
       </c>
       <c r="J13" t="n">
-        <v>61.08</v>
+        <v>59.28</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.14</v>
+        <v>-7.94</v>
       </c>
       <c r="L13" t="n">
-        <v>-5140.55</v>
+        <v>-7936.01</v>
       </c>
     </row>
     <row r="14">
@@ -1250,24 +1250,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
         <v>65.88</v>
       </c>
       <c r="J17" t="n">
-        <v>59.4</v>
+        <v>58.93</v>
       </c>
       <c r="K17" t="n">
-        <v>-9.84</v>
+        <v>-10.55</v>
       </c>
       <c r="L17" t="n">
-        <v>-9836.07</v>
+        <v>-10549.48</v>
       </c>
     </row>
     <row r="18">
@@ -1442,24 +1442,24 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I21" t="n">
         <v>29.09</v>
       </c>
       <c r="J21" t="n">
-        <v>38.98</v>
+        <v>36.02</v>
       </c>
       <c r="K21" t="n">
-        <v>34</v>
+        <v>23.82</v>
       </c>
       <c r="L21" t="n">
-        <v>33997.94</v>
+        <v>23822.62</v>
       </c>
     </row>
     <row r="22">
@@ -1538,24 +1538,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I23" t="n">
         <v>27.84</v>
       </c>
       <c r="J23" t="n">
-        <v>29.58</v>
+        <v>29.08</v>
       </c>
       <c r="K23" t="n">
-        <v>6.25</v>
+        <v>4.45</v>
       </c>
       <c r="L23" t="n">
-        <v>6250</v>
+        <v>4454.02</v>
       </c>
     </row>
   </sheetData>

--- a/result/Table202605.xlsx
+++ b/result/Table202605.xlsx
@@ -754,7 +754,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I7" t="n">
         <v>12.76</v>
       </c>
       <c r="J7" t="n">
-        <v>9.76</v>
+        <v>9.35</v>
       </c>
       <c r="K7" t="n">
-        <v>-23.51</v>
+        <v>-26.72</v>
       </c>
       <c r="L7" t="n">
-        <v>-23510.97</v>
+        <v>-26724.14</v>
       </c>
     </row>
     <row r="8">
@@ -954,7 +954,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -963,19 +963,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I11" t="n">
         <v>10.13</v>
       </c>
       <c r="J11" t="n">
-        <v>7.94</v>
+        <v>7.72</v>
       </c>
       <c r="K11" t="n">
-        <v>-21.62</v>
+        <v>-23.79</v>
       </c>
       <c r="L11" t="n">
-        <v>-21618.95</v>
+        <v>-23790.72</v>
       </c>
     </row>
     <row r="12">

--- a/result/Table202605.xlsx
+++ b/result/Table202605.xlsx
@@ -754,7 +754,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I7" t="n">
         <v>12.76</v>
       </c>
       <c r="J7" t="n">
-        <v>9.35</v>
+        <v>8.91</v>
       </c>
       <c r="K7" t="n">
-        <v>-26.72</v>
+        <v>-30.17</v>
       </c>
       <c r="L7" t="n">
-        <v>-26724.14</v>
+        <v>-30172.41</v>
       </c>
     </row>
     <row r="8">
@@ -954,7 +954,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -963,19 +963,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I11" t="n">
         <v>10.13</v>
       </c>
       <c r="J11" t="n">
-        <v>7.72</v>
+        <v>7.5</v>
       </c>
       <c r="K11" t="n">
-        <v>-23.79</v>
+        <v>-25.96</v>
       </c>
       <c r="L11" t="n">
-        <v>-23790.72</v>
+        <v>-25962.49</v>
       </c>
     </row>
     <row r="12">

--- a/result/Table202605.xlsx
+++ b/result/Table202605.xlsx
@@ -754,7 +754,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -763,19 +763,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I7" t="n">
         <v>12.76</v>
       </c>
       <c r="J7" t="n">
-        <v>8.91</v>
+        <v>8.75</v>
       </c>
       <c r="K7" t="n">
-        <v>-30.17</v>
+        <v>-31.43</v>
       </c>
       <c r="L7" t="n">
-        <v>-30172.41</v>
+        <v>-31426.33</v>
       </c>
     </row>
     <row r="8">
@@ -954,7 +954,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -963,19 +963,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I11" t="n">
         <v>10.13</v>
       </c>
       <c r="J11" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="K11" t="n">
-        <v>-25.96</v>
+        <v>-21.03</v>
       </c>
       <c r="L11" t="n">
-        <v>-25962.49</v>
+        <v>-21026.65</v>
       </c>
     </row>
     <row r="12">
